--- a/platform_PiN_output/Myanmar___MMR/PiN_results_Myanmar___MMR_0907_07AM.xlsx
+++ b/platform_PiN_output/Myanmar___MMR/PiN_results_Myanmar___MMR_0907_07AM.xlsx
@@ -42405,7 +42405,7 @@
       </c>
       <c r="G7" s="34" t="inlineStr">
         <is>
-          <t>07/09/2026 07:53</t>
+          <t>07/09/2026 07:55</t>
         </is>
       </c>
     </row>
